--- a/surveys/testmh/questions.xlsx
+++ b/surveys/testmh/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhaight\Downloads\InterviewGuidesExe\InterviewGuidesExe\surveys\testmh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F69495-2458-49CB-96E1-58B8890A8F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93934BB-3EF3-49ED-9740-78BA668A3FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="Setup" sheetId="1" r:id="rId1"/>
     <sheet name="Questions" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
   <si>
     <t>TestMH</t>
   </si>
@@ -84,6 +97,9 @@
   </si>
   <si>
     <t>Test Question 1</t>
+  </si>
+  <si>
+    <t>Test Question 2</t>
   </si>
 </sst>
 </file>
@@ -103,24 +119,28 @@
       <sz val="10"/>
       <color rgb="FF888888"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF003087"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -173,6 +193,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -180,7 +201,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -492,18 +512,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="5"/>
     </row>
     <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -517,7 +537,7 @@
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -535,7 +555,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -628,6 +648,14 @@
         <v>20</v>
       </c>
     </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="A2:A500" xr:uid="{00000000-0002-0000-0100-000000000000}">
